--- a/testlab/samples/request_check_rule.xlsx
+++ b/testlab/samples/request_check_rule.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Request" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Request" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -774,6 +774,28 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>10.66.66.88</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>192.168.99.99</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>6666</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>P2 - deny o SHARED-PRE: khong the cap phep tu DG, phai sua Shared-PRE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/testlab/samples/request_check_rule.xlsx
+++ b/testlab/samples/request_check_rule.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -796,6 +796,28 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>203.0.113.77</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>192.168.50.91</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>B1 - nguon internet: default route cho ra untrust, rule doi trust -&gt; PHAI chan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/testlab/samples/request_check_rule.xlsx
+++ b/testlab/samples/request_check_rule.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -818,6 +818,28 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>10.10.88.11</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>192.168.88.21</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>9443</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>B3 - deny co service khong resolve duoc: PHAI van canh bao bi chan truoc</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/testlab/samples/request_check_rule.xlsx
+++ b/testlab/samples/request_check_rule.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -840,6 +840,28 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>10.10.44.11</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>192.168.44.21</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>7443</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>B4 - deny o SHARED-POST: them rule vao DG la giai quyet duoc</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
